--- a/apps/sierra-estates-realty/public/downloads/sierra-estates-owners-rent.xlsx
+++ b/apps/sierra-estates-realty/public/downloads/sierra-estates-owners-rent.xlsx
@@ -532,7 +532,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V2" t="str">
-        <v>2026-09-04T14:50:11.188Z</v>
+        <v>2026-09-07T03:58:05.388Z</v>
       </c>
     </row>
     <row r="3">
@@ -668,7 +668,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V4" t="str">
-        <v>2026-09-04T14:50:11.189Z</v>
+        <v>2026-09-07T03:58:05.388Z</v>
       </c>
     </row>
     <row r="5">
@@ -736,7 +736,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V5" t="str">
-        <v>2026-09-04T14:50:11.189Z</v>
+        <v>2026-09-07T03:58:05.388Z</v>
       </c>
     </row>
     <row r="6">
@@ -940,7 +940,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V8" t="str">
-        <v>2026-09-04T14:50:11.189Z</v>
+        <v>2026-09-07T03:58:05.388Z</v>
       </c>
     </row>
     <row r="9">
@@ -1008,7 +1008,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V9" t="str">
-        <v>2026-09-04T14:50:11.189Z</v>
+        <v>2026-09-07T03:58:05.388Z</v>
       </c>
     </row>
     <row r="10">
@@ -1076,7 +1076,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V10" t="str">
-        <v>2026-09-04T14:50:11.189Z</v>
+        <v>2026-09-07T03:58:05.388Z</v>
       </c>
     </row>
     <row r="11">
@@ -1144,7 +1144,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V11" t="str">
-        <v>2026-09-04T14:50:11.189Z</v>
+        <v>2026-09-07T03:58:05.388Z</v>
       </c>
     </row>
     <row r="12">
@@ -1281,7 +1281,7 @@
         <v xml:space="preserve">Owners-Resale </v>
       </c>
       <c r="V13" t="str">
-        <v>2026-09-04T14:50:11.189Z</v>
+        <v>2026-09-07T03:58:05.388Z</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -1364,7 +1364,7 @@
         <v xml:space="preserve">Owners-Resale </v>
       </c>
       <c r="V14" t="str">
-        <v>2026-09-04T14:50:11.189Z</v>
+        <v>2026-09-07T03:58:05.388Z</v>
       </c>
     </row>
     <row r="15">
@@ -3064,7 +3064,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V39" t="str">
-        <v>2026-09-04T14:50:11.190Z</v>
+        <v>2026-09-07T03:58:05.389Z</v>
       </c>
     </row>
     <row r="40">
@@ -3336,7 +3336,7 @@
         <v>Master Inventory 2026</v>
       </c>
       <c r="V43" t="str">
-        <v>2026-09-04T14:50:11.190Z</v>
+        <v>2026-09-07T03:58:05.389Z</v>
       </c>
     </row>
     <row r="44">
@@ -3472,7 +3472,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V45" t="str">
-        <v>2026-09-04T14:50:11.190Z</v>
+        <v>2026-09-07T03:58:05.389Z</v>
       </c>
     </row>
     <row r="46">
@@ -3540,7 +3540,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V46" t="str">
-        <v>2026-09-04T14:50:11.191Z</v>
+        <v>2026-09-07T03:58:05.389Z</v>
       </c>
     </row>
     <row r="47">
@@ -3744,7 +3744,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V49" t="str">
-        <v>2026-09-04T14:50:11.191Z</v>
+        <v>2026-09-07T03:58:05.389Z</v>
       </c>
     </row>
     <row r="50">
@@ -4288,7 +4288,7 @@
         <v>Direct owner</v>
       </c>
       <c r="V57" t="str">
-        <v>2026-09-04T14:50:11.191Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="58">
@@ -6668,7 +6668,7 @@
         <v>Direct owner</v>
       </c>
       <c r="V92" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="93">
@@ -6736,7 +6736,7 @@
         <v>Direct owner</v>
       </c>
       <c r="V93" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="94">
@@ -6804,7 +6804,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V94" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="95">
@@ -6872,7 +6872,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V95" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="96">
@@ -6940,7 +6940,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V96" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="97">
@@ -7008,7 +7008,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V97" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="98">
@@ -7076,7 +7076,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V98" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="99">
@@ -7144,7 +7144,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V99" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="100">
@@ -7348,7 +7348,7 @@
         <v xml:space="preserve">Owners-Resale </v>
       </c>
       <c r="V102" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="103">
@@ -7416,7 +7416,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V103" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="104">
@@ -7484,7 +7484,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V104" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="105">
@@ -7552,7 +7552,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V105" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="106">
@@ -7620,7 +7620,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V106" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="107">
@@ -7688,7 +7688,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V107" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="108">
@@ -7756,7 +7756,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V108" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="109">
@@ -7824,7 +7824,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V109" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="110">
@@ -7892,7 +7892,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V110" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="111">
@@ -7960,7 +7960,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V111" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="112">
@@ -8028,7 +8028,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V112" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="113">
@@ -8096,7 +8096,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V113" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="114">
@@ -8164,7 +8164,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V114" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="115">
@@ -8232,7 +8232,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V115" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="116">
@@ -8300,7 +8300,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V116" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="117">
@@ -8368,7 +8368,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V117" t="str">
-        <v>2026-09-04T14:50:11.192Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="118">
@@ -8436,7 +8436,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V118" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="119">
@@ -8504,7 +8504,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V119" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="120">
@@ -8572,7 +8572,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V120" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="121">
@@ -8640,7 +8640,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V121" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="122">
@@ -8708,7 +8708,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V122" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="123">
@@ -8776,7 +8776,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V123" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="124">
@@ -8844,7 +8844,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V124" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="125">
@@ -8912,7 +8912,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V125" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="126">
@@ -8980,7 +8980,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V126" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="127">
@@ -9048,7 +9048,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V127" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="128">
@@ -9116,7 +9116,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V128" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="129">
@@ -9184,7 +9184,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V129" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="130">
@@ -9252,7 +9252,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V130" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="131">
@@ -9320,7 +9320,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V131" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="132">
@@ -9388,7 +9388,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V132" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="133">
@@ -9456,7 +9456,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V133" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="134">
@@ -9524,7 +9524,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V134" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="135">
@@ -9592,7 +9592,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V135" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="136">
@@ -9660,7 +9660,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V136" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="137">
@@ -9728,7 +9728,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V137" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="138">
@@ -9796,7 +9796,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V138" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="139">
@@ -9864,7 +9864,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V139" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="140">
@@ -9932,7 +9932,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V140" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="141">
@@ -10000,7 +10000,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V141" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="142">
@@ -10068,7 +10068,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V142" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="143">
@@ -10136,7 +10136,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V143" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="144">
@@ -10204,7 +10204,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V144" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="145">
@@ -10272,7 +10272,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V145" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.390Z</v>
       </c>
     </row>
     <row r="146">
@@ -10476,7 +10476,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V148" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="149">
@@ -10544,7 +10544,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V149" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="150">
@@ -10612,7 +10612,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V150" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="151">
@@ -10680,7 +10680,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V151" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="152">
@@ -10748,7 +10748,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V152" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="153">
@@ -10816,7 +10816,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V153" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="154">
@@ -10884,7 +10884,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V154" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="155">
@@ -10952,7 +10952,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V155" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="156">
@@ -11020,7 +11020,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V156" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="157">
@@ -11088,7 +11088,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V157" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="158">
@@ -11156,7 +11156,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V158" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="159">
@@ -11224,7 +11224,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V159" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="160">
@@ -11292,7 +11292,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V160" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="161">
@@ -11360,7 +11360,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V161" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="162">
@@ -11428,7 +11428,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V162" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="163">
@@ -11496,7 +11496,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V163" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="164">
@@ -11564,7 +11564,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V164" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="165">
@@ -11632,7 +11632,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V165" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="166">
@@ -11700,7 +11700,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V166" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="167">
@@ -11768,7 +11768,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V167" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="168">
@@ -11836,7 +11836,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V168" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="169">
@@ -11904,7 +11904,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V169" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="170">
@@ -11972,7 +11972,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V170" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="171">
@@ -12040,7 +12040,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V171" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="172">
@@ -12108,7 +12108,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V172" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="173">
@@ -12176,7 +12176,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V173" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="174">
@@ -12244,7 +12244,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V174" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="175">
@@ -12312,7 +12312,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V175" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="176">
@@ -12380,7 +12380,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V176" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="177">
@@ -12448,7 +12448,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V177" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="178">
@@ -12516,7 +12516,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V178" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="179">
@@ -12584,7 +12584,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V179" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="180">
@@ -12652,7 +12652,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V180" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="181">
@@ -12720,7 +12720,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V181" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="182">
@@ -12788,7 +12788,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V182" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="183">
@@ -12856,7 +12856,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V183" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="184">
@@ -12924,7 +12924,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V184" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="185">
@@ -12992,7 +12992,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V185" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="186">
@@ -13060,7 +13060,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V186" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="187">
@@ -13128,7 +13128,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V187" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="188">
@@ -13196,7 +13196,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V188" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="189">
@@ -13264,7 +13264,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V189" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="190">
@@ -13332,7 +13332,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V190" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="191">
@@ -13400,7 +13400,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V191" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="192">
@@ -13468,7 +13468,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V192" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="193">
@@ -13536,7 +13536,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V193" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="194">
@@ -13604,7 +13604,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V194" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="195">
@@ -13672,7 +13672,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V195" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="196">
@@ -13740,7 +13740,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V196" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="197">
@@ -13808,7 +13808,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V197" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="198">
@@ -13876,7 +13876,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V198" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="199">
@@ -13944,7 +13944,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V199" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="200">
@@ -14012,7 +14012,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V200" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="201">
@@ -14080,7 +14080,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V201" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="202">
@@ -14148,7 +14148,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V202" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="203">
@@ -14216,7 +14216,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V203" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="204">
@@ -14828,7 +14828,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V212" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="213">
@@ -15304,7 +15304,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V219" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="220">
@@ -15372,7 +15372,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V220" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="221">
@@ -15440,7 +15440,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V221" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="222">
@@ -15508,7 +15508,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V222" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="223">
@@ -15576,7 +15576,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V223" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="224">
@@ -15644,7 +15644,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V224" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="225">
@@ -15712,7 +15712,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V225" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="226">
@@ -15780,7 +15780,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V226" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="227">
@@ -15848,7 +15848,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V227" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="228">
@@ -15916,7 +15916,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V228" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="229">
@@ -15984,7 +15984,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V229" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="230">
@@ -16052,7 +16052,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V230" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="231">
@@ -16120,7 +16120,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V231" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="232">
@@ -16188,7 +16188,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V232" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="233">
@@ -16256,7 +16256,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V233" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="234">
@@ -16324,7 +16324,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V234" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="235">
@@ -16392,7 +16392,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V235" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="236">
@@ -16460,7 +16460,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V236" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="237">
@@ -16528,7 +16528,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V237" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="238">
@@ -16596,7 +16596,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V238" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="239">
@@ -16664,7 +16664,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V239" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="240">
@@ -16732,7 +16732,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V240" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="241">
@@ -16800,7 +16800,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V241" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="242">
@@ -16868,7 +16868,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V242" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="243">
@@ -16936,7 +16936,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V243" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="244">
@@ -17004,7 +17004,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V244" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="245">
@@ -17072,7 +17072,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V245" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="246">
@@ -17140,7 +17140,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V246" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="247">
@@ -17208,7 +17208,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V247" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="248">
@@ -17276,7 +17276,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V248" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="249">
@@ -17344,7 +17344,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V249" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="250">
@@ -17412,7 +17412,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V250" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="251">
@@ -17480,7 +17480,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V251" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="252">
@@ -17548,7 +17548,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V252" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="253">
@@ -17616,7 +17616,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V253" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="254">
@@ -17684,7 +17684,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V254" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="255">
@@ -17820,7 +17820,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V256" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="257">
@@ -17888,7 +17888,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V257" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="258">
@@ -17956,7 +17956,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V258" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="259">
@@ -18024,7 +18024,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V259" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="260">
@@ -18092,7 +18092,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V260" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="261">
@@ -18160,7 +18160,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V261" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="262">
@@ -18228,7 +18228,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V262" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="263">
@@ -18296,7 +18296,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V263" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="264">
@@ -18364,7 +18364,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V264" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="265">
@@ -18432,7 +18432,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V265" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="266">
@@ -18500,7 +18500,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V266" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="267">
@@ -18568,7 +18568,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V267" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="268">
@@ -18636,7 +18636,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V268" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="269">
@@ -18704,7 +18704,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V269" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="270">
@@ -18772,7 +18772,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V270" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="271">
@@ -18840,7 +18840,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V271" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="272">
@@ -18908,7 +18908,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V272" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="273">
@@ -18976,7 +18976,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V273" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="274">
@@ -19044,7 +19044,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V274" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="275">
@@ -19112,7 +19112,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V275" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="276">
@@ -19180,7 +19180,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V276" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="277">
@@ -19248,7 +19248,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V277" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="278">
@@ -19316,7 +19316,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V278" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="279">
@@ -19384,7 +19384,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V279" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="280">
@@ -19452,7 +19452,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V280" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="281">
@@ -19520,7 +19520,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V281" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="282">
@@ -19588,7 +19588,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V282" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="283">
@@ -19656,7 +19656,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V283" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="284">
@@ -19724,7 +19724,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V284" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="285">
@@ -19792,7 +19792,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V285" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="286">
@@ -19860,7 +19860,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V286" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="287">
@@ -19928,7 +19928,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V287" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="288">
@@ -19996,7 +19996,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V288" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="289">
@@ -20064,7 +20064,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V289" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="290">
@@ -20132,7 +20132,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V290" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="291">
@@ -20200,7 +20200,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V291" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="292">
@@ -20268,7 +20268,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V292" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="293">
@@ -20336,7 +20336,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V293" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="294">
@@ -20404,7 +20404,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V294" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="295">
@@ -20472,7 +20472,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V295" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="296">
@@ -20540,7 +20540,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V296" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="297">
@@ -20608,7 +20608,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V297" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="298">
@@ -20676,7 +20676,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V298" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="299">
@@ -20744,7 +20744,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V299" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="300">
@@ -20812,7 +20812,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V300" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="301">
@@ -20880,7 +20880,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V301" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="302">
@@ -20948,7 +20948,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V302" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
     <row r="303">
@@ -21016,7 +21016,7 @@
         <v>Owners-Rent</v>
       </c>
       <c r="V303" t="str">
-        <v>2026-09-04T14:50:11.193Z</v>
+        <v>2026-09-07T03:58:05.391Z</v>
       </c>
     </row>
   </sheetData>
